--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920E6008-DAFB-4B41-A9B3-A4D4311CA86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -77,6 +77,39 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>battle.TargetRule</t>
+  </si>
+  <si>
+    <t>Card target rule</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>Self target only</t>
+  </si>
+  <si>
+    <t>battle.EffectType</t>
+  </si>
+  <si>
+    <t>Card effect type</t>
+  </si>
+  <si>
+    <t>ModifyAttribute</t>
+  </si>
+  <si>
+    <t>Modify an attribute</t>
+  </si>
+  <si>
+    <t>battle.Attribute</t>
+  </si>
+  <si>
+    <t>Attribute modifiable by card effect</t>
+  </si>
+  <si>
+    <t>Strength</t>
   </si>
 </sst>
 </file>
@@ -429,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -529,6 +562,75 @@
       </c>
       <c r="L3" s="1"/>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920E6008-DAFB-4B41-A9B3-A4D4311CA86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6DBF38-4CB6-4E9C-8E65-AF94C55A3352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -82,16 +82,28 @@
     <t>battle.TargetRule</t>
   </si>
   <si>
+    <t>Self target only</t>
+  </si>
+  <si>
+    <t>battle.EffectType</t>
+  </si>
+  <si>
+    <t>Modify an attribute</t>
+  </si>
+  <si>
+    <t>battle.Attribute</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
     <t>Card target rule</t>
   </si>
   <si>
     <t>Self</t>
   </si>
   <si>
-    <t>Self target only</t>
-  </si>
-  <si>
-    <t>battle.EffectType</t>
+    <t>Enemy</t>
   </si>
   <si>
     <t>Card effect type</t>
@@ -100,16 +112,19 @@
     <t>ModifyAttribute</t>
   </si>
   <si>
-    <t>Modify an attribute</t>
-  </si>
-  <si>
-    <t>battle.Attribute</t>
+    <t>DealDamage</t>
+  </si>
+  <si>
+    <t>GainBlock</t>
+  </si>
+  <si>
+    <t>ApplyVulnerable</t>
   </si>
   <si>
     <t>Attribute modifiable by card effect</t>
   </si>
   <si>
-    <t>Strength</t>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -462,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -573,44 +588,32 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
@@ -628,7 +631,59 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -131,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,8 +145,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +164,108 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -189,7 +299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -201,6 +311,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,197 +647,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="11">
         <v>19</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" t="b" s="12">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" t="b" s="13">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="14">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="11">
         <v>26</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="13">
         <v>0</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="16">
         <v>27</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="17">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="18">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="11">
         <v>21</v>
       </c>
-      <c r="C6" t="b">
+      <c r="C6" t="b" s="12">
         <v>0</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="b" s="13">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="14">
         <v>28</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="11">
         <v>29</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="13">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="15">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="16">
         <v>30</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="11">
         <v>31</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="16">
         <v>32</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="11">
         <v>23</v>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" t="b" s="12">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" t="b" s="13">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="14">
         <v>33</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="11">
         <v>34</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="16">
         <v>24</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="17">
         <v>1</v>
       </c>
     </row>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R242939a9eecd492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc13f6790b5de4446"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,6 +69,31 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -76,7 +101,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -152,6 +177,154 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -491,12 +664,14 @@
       <x:c r="H4" s="21" t="str">
         <x:v>Self</x:v>
       </x:c>
+      <x:c r="I4"/>
       <x:c r="J4" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="21" t="str">
         <x:v>Self target only</x:v>
       </x:c>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="6"/>
@@ -509,12 +684,14 @@
       <x:c r="H5" s="6" t="str">
         <x:v>Enemy</x:v>
       </x:c>
+      <x:c r="I5"/>
       <x:c r="J5" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K5" s="6" t="str">
         <x:v>Modify an attribute</x:v>
       </x:c>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="6"/>
@@ -527,12 +704,14 @@
       <x:c r="H6" s="6" t="str">
         <x:v>AllEnemies</x:v>
       </x:c>
+      <x:c r="I6"/>
       <x:c r="J6" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
         <x:v>All enemies</x:v>
       </x:c>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="6"/>
@@ -545,12 +724,14 @@
       <x:c r="H7" s="6" t="str">
         <x:v>RandomEnemy</x:v>
       </x:c>
+      <x:c r="I7"/>
       <x:c r="J7" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str">
         <x:v>One deterministic random enemy</x:v>
       </x:c>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="21"/>
@@ -571,12 +752,14 @@
       <x:c r="H8" s="21" t="str">
         <x:v>ModifyAttribute</x:v>
       </x:c>
+      <x:c r="I8"/>
       <x:c r="J8" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="21" t="str">
         <x:v>Strength</x:v>
       </x:c>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="6"/>
@@ -589,9 +772,12 @@
       <x:c r="H9" s="6" t="str">
         <x:v>DealDamage</x:v>
       </x:c>
+      <x:c r="I9"/>
       <x:c r="J9" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="6"/>
@@ -604,9 +790,12 @@
       <x:c r="H10" s="6" t="str">
         <x:v>GainBlock</x:v>
       </x:c>
+      <x:c r="I10"/>
       <x:c r="J10" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="6"/>
@@ -619,455 +808,2356 @@
       <x:c r="H11" s="6" t="str">
         <x:v>ApplyVulnerable</x:v>
       </x:c>
+      <x:c r="I11"/>
       <x:c r="J11" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="21"/>
-      <x:c r="B12" s="21" t="str">
+      <x:c r="A12" s="32"/>
+      <x:c r="B12" s="32"/>
+      <x:c r="C12" s="32"/>
+      <x:c r="D12" s="32"/>
+      <x:c r="E12" s="32"/>
+      <x:c r="F12" s="32"/>
+      <x:c r="G12" s="32"/>
+      <x:c r="H12" s="32" t="str">
+        <x:v>DrawCards</x:v>
+      </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="str">
+        <x:v>Card draw</x:v>
+      </x:c>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="32"/>
+      <x:c r="B13" s="32"/>
+      <x:c r="C13" s="32"/>
+      <x:c r="D13" s="32"/>
+      <x:c r="E13" s="32"/>
+      <x:c r="F13" s="32"/>
+      <x:c r="G13" s="32"/>
+      <x:c r="H13" s="32" t="str">
+        <x:v>ExhaustSelectedHandCard</x:v>
+      </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="str">
+        <x:v>Exhaust one explicitly selected hand card</x:v>
+      </x:c>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14" s="45" t="str">
+        <x:v>Heal</x:v>
+      </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14" s="45" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K14" s="45"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15" s="32" t="str">
+        <x:v>DealDamageFromSourceBlock</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15" s="32" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K15" s="32" t="str">
+        <x:v>Deal damage equal to source current Block</x:v>
+      </x:c>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16" s="60"/>
+      <x:c r="C16" s="60"/>
+      <x:c r="D16" s="60"/>
+      <x:c r="E16"/>
+      <x:c r="F16" s="60"/>
+      <x:c r="G16"/>
+      <x:c r="H16" s="60" t="str">
+        <x:v>RetainBlock</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16" s="60" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17" s="32" t="str">
+        <x:v>PlayTopDrawCardAndExhaust</x:v>
+      </x:c>
+      <x:c r="I17"/>
+      <x:c r="J17" s="32" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>Play the top Draw Pile card and Exhaust it</x:v>
+      </x:c>
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18"/>
+      <x:c r="B18" s="60"/>
+      <x:c r="C18" s="60"/>
+      <x:c r="D18" s="60"/>
+      <x:c r="E18"/>
+      <x:c r="F18" s="60"/>
+      <x:c r="G18"/>
+      <x:c r="H18" s="60" t="str">
+        <x:v>RegisterBlockGainRandomEnemyDamage</x:v>
+      </x:c>
+      <x:c r="I18"/>
+      <x:c r="J18" s="60" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K18" s="60" t="str">
+        <x:v>Whenever the source gains Block, deal the configured damage to one random living enemy</x:v>
+      </x:c>
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19"/>
+      <x:c r="B19" t="str">
         <x:v>battle.Attribute</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="b">
+      <x:c r="C19" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="22" t="b">
+      <x:c r="D19" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E12" s="21"/>
-      <x:c r="F12" s="21" t="str">
+      <x:c r="E19"/>
+      <x:c r="F19" t="str">
         <x:v>Attribute modifiable by card effect</x:v>
       </x:c>
-      <x:c r="G12" s="21"/>
-      <x:c r="H12" s="21" t="str">
+      <x:c r="G19"/>
+      <x:c r="H19" s="32" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="J12" s="21" t="n">
+      <x:c r="I19"/>
+      <x:c r="J19" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6"/>
-      <x:c r="D13" s="6"/>
-      <x:c r="E13" s="6"/>
-      <x:c r="F13" s="6"/>
-      <x:c r="G13" s="6"/>
-      <x:c r="H13" s="6" t="str">
+      <x:c r="K19" s="32"/>
+      <x:c r="L19"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20" s="32" t="str">
         <x:v>Strength</x:v>
       </x:c>
-      <x:c r="J13" s="6" t="n">
+      <x:c r="I20"/>
+      <x:c r="J20" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="21"/>
-      <x:c r="B14" s="21" t="str">
+      <x:c r="K20" s="32"/>
+      <x:c r="L20"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21" t="str">
         <x:v>battle.EnemyIntentType</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="b">
+      <x:c r="C21" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="22" t="b">
+      <x:c r="D21" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E14" s="21"/>
-      <x:c r="F14" s="21" t="str">
+      <x:c r="E21"/>
+      <x:c r="F21" t="str">
         <x:v>Enemy intent type</x:v>
       </x:c>
-      <x:c r="G14" s="21"/>
-      <x:c r="H14" s="21" t="str">
+      <x:c r="G21"/>
+      <x:c r="H21" s="32" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="J14" s="21" t="n">
+      <x:c r="I21"/>
+      <x:c r="J21" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="21" t="str">
+      <x:c r="K21" s="32" t="str">
         <x:v>Attack intent</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="6"/>
-      <x:c r="B15" s="6"/>
-      <x:c r="C15" s="6"/>
-      <x:c r="D15" s="6"/>
-      <x:c r="E15" s="6"/>
-      <x:c r="F15" s="6"/>
-      <x:c r="G15" s="6"/>
-      <x:c r="H15" s="6" t="str">
+      <x:c r="L21"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22" s="32" t="str">
         <x:v>Defend</x:v>
       </x:c>
-      <x:c r="J15" s="6" t="n">
+      <x:c r="I22"/>
+      <x:c r="J22" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="6" t="str">
+      <x:c r="K22" s="32" t="str">
         <x:v>Defend intent</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="6"/>
-      <x:c r="B16" s="6"/>
-      <x:c r="C16" s="6"/>
-      <x:c r="D16" s="6"/>
-      <x:c r="E16" s="6"/>
-      <x:c r="F16" s="6"/>
-      <x:c r="G16" s="6"/>
-      <x:c r="H16" s="6" t="str">
+      <x:c r="L22"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23"/>
+      <x:c r="B23" s="60"/>
+      <x:c r="C23" s="60"/>
+      <x:c r="D23" s="60"/>
+      <x:c r="E23"/>
+      <x:c r="F23" s="60"/>
+      <x:c r="G23"/>
+      <x:c r="H23" s="60" t="str">
         <x:v>Buff</x:v>
       </x:c>
-      <x:c r="J16" s="6" t="n">
+      <x:c r="I23"/>
+      <x:c r="J23" s="60" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K16" s="6" t="str">
+      <x:c r="K23" s="60" t="str">
         <x:v>Buff intent</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="6"/>
-      <x:c r="B17" s="6"/>
-      <x:c r="C17" s="6"/>
-      <x:c r="D17" s="6"/>
-      <x:c r="E17" s="6"/>
-      <x:c r="F17" s="6"/>
-      <x:c r="G17" s="6"/>
-      <x:c r="H17" s="6" t="str">
+      <x:c r="L23"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24" s="32" t="str">
         <x:v>Debuff</x:v>
       </x:c>
-      <x:c r="J17" s="6" t="n">
+      <x:c r="I24"/>
+      <x:c r="J24" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K17" s="6" t="str">
+      <x:c r="K24" s="32" t="str">
         <x:v>Debuff intent</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="6"/>
-      <x:c r="B18" s="6"/>
-      <x:c r="C18" s="6"/>
-      <x:c r="D18" s="6"/>
-      <x:c r="E18" s="6"/>
-      <x:c r="F18" s="6"/>
-      <x:c r="G18" s="6"/>
-      <x:c r="H18" s="6" t="str">
+      <x:c r="L24"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25"/>
+      <x:c r="B25" s="60"/>
+      <x:c r="C25" s="60"/>
+      <x:c r="D25" s="60"/>
+      <x:c r="E25"/>
+      <x:c r="F25" s="60"/>
+      <x:c r="G25"/>
+      <x:c r="H25" s="60" t="str">
         <x:v>Special</x:v>
       </x:c>
-      <x:c r="J18" s="6" t="n">
+      <x:c r="I25"/>
+      <x:c r="J25" s="60" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K18" s="6" t="str">
+      <x:c r="K25" s="60" t="str">
         <x:v>Special intent</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="22" customHeight="1">
-      <x:c r="A19" s="21"/>
-      <x:c r="B19" s="21" t="str">
+      <x:c r="L25"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26"/>
+      <x:c r="B26" t="str">
         <x:v>battle.CardImplementationStatus</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="str">
+      <x:c r="C26" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="21" t="str">
+      <x:c r="D26" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E19" s="21"/>
-      <x:c r="F19" s="21" t="str">
+      <x:c r="E26"/>
+      <x:c r="F26" t="str">
         <x:v>Card implementation status</x:v>
       </x:c>
-      <x:c r="G19" s="21"/>
-      <x:c r="H19" s="21" t="str">
+      <x:c r="G26"/>
+      <x:c r="H26" s="32" t="str">
         <x:v>Implemented</x:v>
       </x:c>
-      <x:c r="J19" s="21" t="str">
+      <x:c r="I26"/>
+      <x:c r="J26" s="32" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="21" t="str">
+      <x:c r="K26" s="32" t="str">
         <x:v>Fully implemented and playable</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="6"/>
-      <x:c r="B20" s="6"/>
-      <x:c r="C20" s="6"/>
-      <x:c r="D20" s="6"/>
-      <x:c r="E20" s="6"/>
-      <x:c r="F20" s="6"/>
-      <x:c r="G20" s="6"/>
-      <x:c r="H20" s="6" t="str">
+      <x:c r="L26"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27" s="32" t="str">
         <x:v>CatalogOnly</x:v>
       </x:c>
-      <x:c r="J20" s="6" t="str">
+      <x:c r="I27"/>
+      <x:c r="J27" s="32" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K20" s="6" t="str">
+      <x:c r="K27" s="32" t="str">
         <x:v>Catalog entry blocked from play</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="21"/>
-      <x:c r="B21" s="21" t="str">
+      <x:c r="L27"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28"/>
+      <x:c r="B28" s="60" t="str">
         <x:v>battle.CardType</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="b">
+      <x:c r="C28" s="60" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D21" s="22" t="b">
+      <x:c r="D28" s="60" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E21" s="21"/>
-      <x:c r="F21" s="21" t="str">
+      <x:c r="E28"/>
+      <x:c r="F28" s="60" t="str">
         <x:v>Catalog card type</x:v>
       </x:c>
-      <x:c r="G21" s="21"/>
-      <x:c r="H21" s="21" t="str">
+      <x:c r="G28"/>
+      <x:c r="H28" s="60" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="J21" s="21" t="n">
+      <x:c r="I28"/>
+      <x:c r="J28" s="60" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="21" t="str">
+      <x:c r="K28" s="60" t="str">
         <x:v>Attack card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="6"/>
-      <x:c r="B22" s="6"/>
-      <x:c r="C22" s="6"/>
-      <x:c r="D22" s="6"/>
-      <x:c r="E22" s="6"/>
-      <x:c r="F22" s="6"/>
-      <x:c r="G22" s="6"/>
-      <x:c r="H22" s="6" t="str">
+      <x:c r="L28"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29" s="32" t="str">
         <x:v>Skill</x:v>
       </x:c>
-      <x:c r="J22" s="6" t="n">
+      <x:c r="I29"/>
+      <x:c r="J29" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K22" s="6" t="str">
+      <x:c r="K29" s="32" t="str">
         <x:v>Skill card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="22" customHeight="1">
-      <x:c r="A23" s="6"/>
-      <x:c r="B23" s="6"/>
-      <x:c r="C23" s="6"/>
-      <x:c r="D23" s="6"/>
-      <x:c r="E23" s="6"/>
-      <x:c r="F23" s="6"/>
-      <x:c r="G23" s="6"/>
-      <x:c r="H23" s="6" t="str">
+      <x:c r="L29"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30" s="32" t="str">
         <x:v>Power</x:v>
       </x:c>
-      <x:c r="J23" s="6" t="n">
+      <x:c r="I30"/>
+      <x:c r="J30" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K23" s="6" t="str">
+      <x:c r="K30" s="32" t="str">
         <x:v>Power card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="21"/>
-      <x:c r="B24" s="21" t="str">
+      <x:c r="L30"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31"/>
+      <x:c r="B31" t="str">
         <x:v>battle.CardRarity</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="b">
+      <x:c r="C31" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D24" s="22" t="b">
+      <x:c r="D31" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E24" s="21"/>
-      <x:c r="F24" s="21" t="str">
+      <x:c r="E31"/>
+      <x:c r="F31" t="str">
         <x:v>Catalog card rarity</x:v>
       </x:c>
-      <x:c r="G24" s="21"/>
-      <x:c r="H24" s="21" t="str">
+      <x:c r="G31"/>
+      <x:c r="H31" s="32" t="str">
         <x:v>Basic</x:v>
       </x:c>
-      <x:c r="J24" s="21" t="n">
+      <x:c r="I31"/>
+      <x:c r="J31" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="21" t="str">
+      <x:c r="K31" s="32" t="str">
         <x:v>Basic card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="22" customHeight="1">
-      <x:c r="A25" s="6"/>
-      <x:c r="B25" s="6"/>
-      <x:c r="C25" s="6"/>
-      <x:c r="D25" s="6"/>
-      <x:c r="E25" s="6"/>
-      <x:c r="F25" s="6"/>
-      <x:c r="G25" s="6"/>
-      <x:c r="H25" s="6" t="str">
+      <x:c r="L31"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32" s="32" t="str">
         <x:v>Common</x:v>
       </x:c>
-      <x:c r="J25" s="6" t="n">
+      <x:c r="I32"/>
+      <x:c r="J32" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K25" s="6" t="str">
+      <x:c r="K32" s="32" t="str">
         <x:v>Common card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="6"/>
-      <x:c r="B26" s="6"/>
-      <x:c r="C26" s="6"/>
-      <x:c r="D26" s="6"/>
-      <x:c r="E26" s="6"/>
-      <x:c r="F26" s="6"/>
-      <x:c r="G26" s="6"/>
-      <x:c r="H26" s="6" t="str">
+      <x:c r="L32"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33"/>
+      <x:c r="B33" s="60"/>
+      <x:c r="C33" s="60"/>
+      <x:c r="D33" s="60"/>
+      <x:c r="E33"/>
+      <x:c r="F33" s="60"/>
+      <x:c r="G33"/>
+      <x:c r="H33" s="60" t="str">
         <x:v>Uncommon</x:v>
       </x:c>
-      <x:c r="J26" s="6" t="n">
+      <x:c r="I33"/>
+      <x:c r="J33" s="60" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K26" s="6" t="str">
+      <x:c r="K33" s="60" t="str">
         <x:v>Uncommon card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="22" customHeight="1">
-      <x:c r="A27" s="6"/>
-      <x:c r="B27" s="6"/>
-      <x:c r="C27" s="6"/>
-      <x:c r="D27" s="6"/>
-      <x:c r="E27" s="6"/>
-      <x:c r="F27" s="6"/>
-      <x:c r="G27" s="6"/>
-      <x:c r="H27" s="6" t="str">
+      <x:c r="L33"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34" s="32" t="str">
         <x:v>Rare</x:v>
       </x:c>
-      <x:c r="J27" s="6" t="n">
+      <x:c r="I34"/>
+      <x:c r="J34" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K27" s="6" t="str">
+      <x:c r="K34" s="32" t="str">
         <x:v>Rare card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="6"/>
-      <x:c r="B28" s="6"/>
-      <x:c r="C28" s="6"/>
-      <x:c r="D28" s="6"/>
-      <x:c r="E28" s="6"/>
-      <x:c r="F28" s="6"/>
-      <x:c r="G28" s="6"/>
-      <x:c r="H28" s="6" t="str">
+      <x:c r="L34"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35"/>
+      <x:c r="B35" s="60"/>
+      <x:c r="C35" s="60"/>
+      <x:c r="D35" s="60"/>
+      <x:c r="E35"/>
+      <x:c r="F35" s="60"/>
+      <x:c r="G35"/>
+      <x:c r="H35" s="60" t="str">
         <x:v>Ancient</x:v>
       </x:c>
-      <x:c r="J28" s="6" t="n">
+      <x:c r="I35"/>
+      <x:c r="J35" s="60" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K28" s="6" t="str">
+      <x:c r="K35" s="60" t="str">
         <x:v>Ancient card</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="22" customHeight="1">
-      <x:c r="A29" s="21"/>
-      <x:c r="B29" s="21" t="str">
+      <x:c r="L35"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36"/>
+      <x:c r="B36" t="str">
         <x:v>battle.CardCostKind</x:v>
       </x:c>
-      <x:c r="C29" s="22" t="b">
+      <x:c r="C36" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="22" t="b">
+      <x:c r="D36" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E29" s="21"/>
-      <x:c r="F29" s="21" t="str">
+      <x:c r="E36"/>
+      <x:c r="F36" t="str">
         <x:v>Card energy cost kind</x:v>
       </x:c>
-      <x:c r="G29" s="21"/>
-      <x:c r="H29" s="21" t="str">
+      <x:c r="G36"/>
+      <x:c r="H36" s="32" t="str">
         <x:v>Fixed</x:v>
       </x:c>
-      <x:c r="J29" s="21" t="n">
+      <x:c r="I36"/>
+      <x:c r="J36" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="21" t="str">
+      <x:c r="K36" s="32" t="str">
         <x:v>Fixed integer cost</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="6"/>
-      <x:c r="B30" s="6"/>
-      <x:c r="C30" s="6"/>
-      <x:c r="D30" s="6"/>
-      <x:c r="E30" s="6"/>
-      <x:c r="F30" s="6"/>
-      <x:c r="G30" s="6"/>
-      <x:c r="H30" s="6" t="str">
+      <x:c r="L36"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37" s="32" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="J30" s="6" t="n">
+      <x:c r="I37"/>
+      <x:c r="J37" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K30" s="6" t="str">
+      <x:c r="K37" s="32" t="str">
         <x:v>Variable X cost</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="22" customHeight="1">
-      <x:c r="A31" s="21"/>
-      <x:c r="B31" s="21" t="str">
+      <x:c r="L37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38" s="61" t="str">
         <x:v>battle.CardPlayDestination</x:v>
       </x:c>
-      <x:c r="C31" s="22" t="b">
+      <x:c r="C38" s="61" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D31" s="22" t="b">
+      <x:c r="D38" s="61" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E31" s="21"/>
-      <x:c r="F31" s="21" t="str">
+      <x:c r="E38"/>
+      <x:c r="F38" s="61" t="str">
         <x:v>Successful card play destination</x:v>
       </x:c>
-      <x:c r="G31" s="21"/>
-      <x:c r="H31" s="21" t="str">
+      <x:c r="G38"/>
+      <x:c r="H38" s="61" t="str">
         <x:v>DiscardPile</x:v>
       </x:c>
-      <x:c r="J31" s="21" t="n">
+      <x:c r="I38"/>
+      <x:c r="J38" s="61" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="21" t="str">
+      <x:c r="K38" s="61" t="str">
         <x:v>Move to discard pile</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="6"/>
-      <x:c r="B32" s="6"/>
-      <x:c r="C32" s="6"/>
-      <x:c r="D32" s="6"/>
-      <x:c r="E32" s="6"/>
-      <x:c r="F32" s="6"/>
-      <x:c r="G32" s="6"/>
-      <x:c r="H32" s="6" t="str">
+      <x:c r="L38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39" s="40" t="str">
         <x:v>ExhaustPile</x:v>
       </x:c>
-      <x:c r="J32" s="6" t="n">
+      <x:c r="I39"/>
+      <x:c r="J39" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K32" s="6" t="str">
+      <x:c r="K39" s="40" t="str">
         <x:v>Move to exhaust pile</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="22" customHeight="1">
-      <x:c r="A33" s="6"/>
-      <x:c r="B33" s="6"/>
-      <x:c r="C33" s="6"/>
-      <x:c r="D33" s="6"/>
-      <x:c r="E33" s="6"/>
-      <x:c r="F33" s="6"/>
-      <x:c r="G33" s="6"/>
-      <x:c r="H33" s="6" t="str">
+      <x:c r="L39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40" s="61"/>
+      <x:c r="C40" s="61"/>
+      <x:c r="D40" s="61"/>
+      <x:c r="E40"/>
+      <x:c r="F40" s="61"/>
+      <x:c r="G40"/>
+      <x:c r="H40" s="61" t="str">
         <x:v>Power</x:v>
       </x:c>
-      <x:c r="J33" s="6" t="n">
+      <x:c r="I40"/>
+      <x:c r="J40" s="61" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K33" s="6" t="str">
+      <x:c r="K40" s="61" t="str">
         <x:v>Become a power</x:v>
       </x:c>
+      <x:c r="L40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41"/>
+      <x:c r="B41" t="str">
+        <x:v>battle.HeroRuntimeProfile</x:v>
+      </x:c>
+      <x:c r="C41" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41"/>
+      <x:c r="F41" t="str">
+        <x:v>Battle hero runtime profile</x:v>
+      </x:c>
+      <x:c r="G41"/>
+      <x:c r="H41" s="40" t="str">
+        <x:v>Legacy</x:v>
+      </x:c>
+      <x:c r="I41"/>
+      <x:c r="J41" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41" s="40" t="str">
+        <x:v>Use the existing battle runtime</x:v>
+      </x:c>
+      <x:c r="L41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+      <x:c r="G42"/>
+      <x:c r="H42" s="40" t="str">
+        <x:v>MachineGunner</x:v>
+      </x:c>
+      <x:c r="I42"/>
+      <x:c r="J42" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K42" s="40" t="str">
+        <x:v>Use the machine gunner battle runtime</x:v>
+      </x:c>
+      <x:c r="L42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43"/>
+      <x:c r="B43" t="str">
+        <x:v>battle.MachineGunnerProgramId</x:v>
+      </x:c>
+      <x:c r="C43" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43"/>
+      <x:c r="F43" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="G43"/>
+      <x:c r="H43" s="40" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I43"/>
+      <x:c r="J43" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" s="40" t="str">
+        <x:v>No machine gunner program</x:v>
+      </x:c>
+      <x:c r="L43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44"/>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44" s="40" t="str">
+        <x:v>Shoot</x:v>
+      </x:c>
+      <x:c r="I44"/>
+      <x:c r="J44" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K44" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45" s="40" t="str">
+        <x:v>Elbow</x:v>
+      </x:c>
+      <x:c r="I45"/>
+      <x:c r="J45" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46"/>
+      <x:c r="B46"/>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46" s="40" t="str">
+        <x:v>Block</x:v>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K46" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47" s="40" t="str">
+        <x:v>Reload</x:v>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47" s="40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K47" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48" s="40" t="str">
+        <x:v>Stim</x:v>
+      </x:c>
+      <x:c r="I48"/>
+      <x:c r="J48" s="40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K48" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+      <x:c r="G49"/>
+      <x:c r="H49" s="40" t="str">
+        <x:v>CoreExpansion</x:v>
+      </x:c>
+      <x:c r="I49"/>
+      <x:c r="J49" s="40" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K49" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+      <x:c r="G50"/>
+      <x:c r="H50" s="40" t="str">
+        <x:v>OutputAdjust</x:v>
+      </x:c>
+      <x:c r="I50"/>
+      <x:c r="J50" s="40" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K50" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51" s="40" t="str">
+        <x:v>BlastShield</x:v>
+      </x:c>
+      <x:c r="I51"/>
+      <x:c r="J51" s="40" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K51" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
+      <x:c r="G52"/>
+      <x:c r="H52" s="40" t="str">
+        <x:v>MagExpansion</x:v>
+      </x:c>
+      <x:c r="I52"/>
+      <x:c r="J52" s="40" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K52" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
+      <x:c r="F53"/>
+      <x:c r="G53"/>
+      <x:c r="H53" s="40" t="str">
+        <x:v>IncendiaryAmmo</x:v>
+      </x:c>
+      <x:c r="I53"/>
+      <x:c r="J53" s="40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K53" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54"/>
+      <x:c r="G54"/>
+      <x:c r="H54" s="40" t="str">
+        <x:v>SmokePersist</x:v>
+      </x:c>
+      <x:c r="I54"/>
+      <x:c r="J54" s="40" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K54" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55"/>
+      <x:c r="G55"/>
+      <x:c r="H55" s="40" t="str">
+        <x:v>KungfuMech</x:v>
+      </x:c>
+      <x:c r="I55"/>
+      <x:c r="J55" s="40" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K55" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56"/>
+      <x:c r="B56"/>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56"/>
+      <x:c r="G56"/>
+      <x:c r="H56" s="40" t="str">
+        <x:v>Overload</x:v>
+      </x:c>
+      <x:c r="I56"/>
+      <x:c r="J56" s="40" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K56" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57"/>
+      <x:c r="G57"/>
+      <x:c r="H57" s="40" t="str">
+        <x:v>TumbleReload</x:v>
+      </x:c>
+      <x:c r="I57"/>
+      <x:c r="J57" s="40" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K57" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58"/>
+      <x:c r="G58"/>
+      <x:c r="H58" s="40" t="str">
+        <x:v>StunGrenade</x:v>
+      </x:c>
+      <x:c r="I58"/>
+      <x:c r="J58" s="40" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K58" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59"/>
+      <x:c r="G59"/>
+      <x:c r="H59" s="40" t="str">
+        <x:v>Retreat</x:v>
+      </x:c>
+      <x:c r="I59"/>
+      <x:c r="J59" s="40" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K59" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60"/>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
+      <x:c r="E60"/>
+      <x:c r="F60"/>
+      <x:c r="G60"/>
+      <x:c r="H60" s="40" t="str">
+        <x:v>GasPump</x:v>
+      </x:c>
+      <x:c r="I60"/>
+      <x:c r="J60" s="40" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K60" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61"/>
+      <x:c r="B61"/>
+      <x:c r="C61"/>
+      <x:c r="D61"/>
+      <x:c r="E61"/>
+      <x:c r="F61"/>
+      <x:c r="G61"/>
+      <x:c r="H61" s="40" t="str">
+        <x:v>Napalm</x:v>
+      </x:c>
+      <x:c r="I61"/>
+      <x:c r="J61" s="40" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K61" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62"/>
+      <x:c r="B62"/>
+      <x:c r="C62"/>
+      <x:c r="D62"/>
+      <x:c r="E62"/>
+      <x:c r="F62"/>
+      <x:c r="G62"/>
+      <x:c r="H62" s="40" t="str">
+        <x:v>Molotov</x:v>
+      </x:c>
+      <x:c r="I62"/>
+      <x:c r="J62" s="40" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K62" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63"/>
+      <x:c r="C63"/>
+      <x:c r="D63"/>
+      <x:c r="E63"/>
+      <x:c r="F63"/>
+      <x:c r="G63"/>
+      <x:c r="H63" s="40" t="str">
+        <x:v>HoldLine</x:v>
+      </x:c>
+      <x:c r="I63"/>
+      <x:c r="J63" s="40" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K63" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64"/>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
+      <x:c r="E64"/>
+      <x:c r="F64"/>
+      <x:c r="G64"/>
+      <x:c r="H64" s="40" t="str">
+        <x:v>SmokeBomb</x:v>
+      </x:c>
+      <x:c r="I64"/>
+      <x:c r="J64" s="40" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K64" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65"/>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
+      <x:c r="E65"/>
+      <x:c r="F65"/>
+      <x:c r="G65"/>
+      <x:c r="H65" s="40" t="str">
+        <x:v>IncompleteCombustion</x:v>
+      </x:c>
+      <x:c r="I65"/>
+      <x:c r="J65" s="40" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K65" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66" s="40" t="str">
+        <x:v>KnockbackShot</x:v>
+      </x:c>
+      <x:c r="I66"/>
+      <x:c r="J66" s="40" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K66" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67" s="40" t="str">
+        <x:v>Spray</x:v>
+      </x:c>
+      <x:c r="I67"/>
+      <x:c r="J67" s="40" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K67" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+      <x:c r="G68"/>
+      <x:c r="H68" s="40" t="str">
+        <x:v>BayonetParry</x:v>
+      </x:c>
+      <x:c r="I68"/>
+      <x:c r="J68" s="40" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K68" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69" s="40" t="str">
+        <x:v>WildRampage</x:v>
+      </x:c>
+      <x:c r="I69"/>
+      <x:c r="J69" s="40" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K69" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70" s="40" t="str">
+        <x:v>QuickElbow</x:v>
+      </x:c>
+      <x:c r="I70"/>
+      <x:c r="J70" s="40" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K70" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71" s="40" t="str">
+        <x:v>KidneyShot</x:v>
+      </x:c>
+      <x:c r="I71"/>
+      <x:c r="J71" s="40" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K71" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72"/>
+      <x:c r="B72"/>
+      <x:c r="C72"/>
+      <x:c r="D72"/>
+      <x:c r="E72"/>
+      <x:c r="F72"/>
+      <x:c r="G72"/>
+      <x:c r="H72" s="40" t="str">
+        <x:v>PainfulElbow</x:v>
+      </x:c>
+      <x:c r="I72"/>
+      <x:c r="J72" s="40" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K72" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73"/>
+      <x:c r="B73"/>
+      <x:c r="C73"/>
+      <x:c r="D73"/>
+      <x:c r="E73"/>
+      <x:c r="F73"/>
+      <x:c r="G73"/>
+      <x:c r="H73" s="40" t="str">
+        <x:v>HeavyElbow</x:v>
+      </x:c>
+      <x:c r="I73"/>
+      <x:c r="J73" s="40" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K73" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74"/>
+      <x:c r="B74"/>
+      <x:c r="C74"/>
+      <x:c r="D74"/>
+      <x:c r="E74"/>
+      <x:c r="F74"/>
+      <x:c r="G74"/>
+      <x:c r="H74" s="40" t="str">
+        <x:v>FieldSurgery</x:v>
+      </x:c>
+      <x:c r="I74"/>
+      <x:c r="J74" s="40" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K74" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75"/>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+      <x:c r="H75" s="40" t="str">
+        <x:v>HurricaneElbow</x:v>
+      </x:c>
+      <x:c r="I75"/>
+      <x:c r="J75" s="40" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K75" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+      <x:c r="H76" s="40" t="str">
+        <x:v>PrecisionShot</x:v>
+      </x:c>
+      <x:c r="I76"/>
+      <x:c r="J76" s="40" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K76" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77"/>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+      <x:c r="H77" s="40" t="str">
+        <x:v>TacticalAdvance</x:v>
+      </x:c>
+      <x:c r="I77"/>
+      <x:c r="J77" s="40" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K77" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78"/>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+      <x:c r="H78" s="40" t="str">
+        <x:v>QuickRoll</x:v>
+      </x:c>
+      <x:c r="I78"/>
+      <x:c r="J78" s="40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K78" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+      <x:c r="H79" s="40" t="str">
+        <x:v>ElectroBoost</x:v>
+      </x:c>
+      <x:c r="I79"/>
+      <x:c r="J79" s="40" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K79" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+      <x:c r="H80" s="40" t="str">
+        <x:v>GuidedNuke</x:v>
+      </x:c>
+      <x:c r="I80"/>
+      <x:c r="J80" s="40" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K80" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+      <x:c r="H81" s="40" t="str">
+        <x:v>BansheeStrike</x:v>
+      </x:c>
+      <x:c r="I81"/>
+      <x:c r="J81" s="40" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K81" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
+      <x:c r="H82" s="40" t="str">
+        <x:v>FireSupport</x:v>
+      </x:c>
+      <x:c r="I82"/>
+      <x:c r="J82" s="40" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K82" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
+      <x:c r="G83"/>
+      <x:c r="H83" s="40" t="str">
+        <x:v>FireBombardment</x:v>
+      </x:c>
+      <x:c r="I83"/>
+      <x:c r="J83" s="40" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K83" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+      <x:c r="H84" s="40" t="str">
+        <x:v>FiveHundredPounder</x:v>
+      </x:c>
+      <x:c r="I84"/>
+      <x:c r="J84" s="40" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K84" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
+      <x:c r="H85" s="40" t="str">
+        <x:v>ComboElbow</x:v>
+      </x:c>
+      <x:c r="I85"/>
+      <x:c r="J85" s="40" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K85" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
+      <x:c r="H86" s="40" t="str">
+        <x:v>OpportunisticStrike</x:v>
+      </x:c>
+      <x:c r="I86"/>
+      <x:c r="J86" s="40" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K86" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+      <x:c r="H87" s="40" t="str">
+        <x:v>VentHeat</x:v>
+      </x:c>
+      <x:c r="I87"/>
+      <x:c r="J87" s="40" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K87" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88"/>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+      <x:c r="G88"/>
+      <x:c r="H88" s="40" t="str">
+        <x:v>PowerOverclock</x:v>
+      </x:c>
+      <x:c r="I88"/>
+      <x:c r="J88" s="40" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K88" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89" s="40" t="str">
+        <x:v>Garrison</x:v>
+      </x:c>
+      <x:c r="I89"/>
+      <x:c r="J89" s="40" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K89" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90"/>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
+      <x:c r="H90" s="40" t="str">
+        <x:v>SniperShot</x:v>
+      </x:c>
+      <x:c r="I90"/>
+      <x:c r="J90" s="40" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K90" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91"/>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
+      <x:c r="H91" s="40" t="str">
+        <x:v>SpikeShot</x:v>
+      </x:c>
+      <x:c r="I91"/>
+      <x:c r="J91" s="40" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K91" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92"/>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
+      <x:c r="H92" s="40" t="str">
+        <x:v>OpticalCamo</x:v>
+      </x:c>
+      <x:c r="I92"/>
+      <x:c r="J92" s="40" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K92" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93"/>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
+      <x:c r="H93" s="40" t="str">
+        <x:v>Unstoppable</x:v>
+      </x:c>
+      <x:c r="I93"/>
+      <x:c r="J93" s="40" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K93" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94"/>
+      <x:c r="B94"/>
+      <x:c r="C94"/>
+      <x:c r="D94"/>
+      <x:c r="E94"/>
+      <x:c r="F94"/>
+      <x:c r="G94"/>
+      <x:c r="H94" s="40" t="str">
+        <x:v>GuerrillaTactics</x:v>
+      </x:c>
+      <x:c r="I94"/>
+      <x:c r="J94" s="40" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K94" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95"/>
+      <x:c r="B95"/>
+      <x:c r="C95"/>
+      <x:c r="D95"/>
+      <x:c r="E95"/>
+      <x:c r="F95"/>
+      <x:c r="G95"/>
+      <x:c r="H95" s="40" t="str">
+        <x:v>ExplosiveElbow</x:v>
+      </x:c>
+      <x:c r="I95"/>
+      <x:c r="J95" s="40" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K95" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96"/>
+      <x:c r="B96"/>
+      <x:c r="C96"/>
+      <x:c r="D96"/>
+      <x:c r="E96"/>
+      <x:c r="F96"/>
+      <x:c r="G96"/>
+      <x:c r="H96" s="40" t="str">
+        <x:v>AgedOil</x:v>
+      </x:c>
+      <x:c r="I96"/>
+      <x:c r="J96" s="40" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K96" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97"/>
+      <x:c r="B97"/>
+      <x:c r="C97"/>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
+      <x:c r="F97"/>
+      <x:c r="G97"/>
+      <x:c r="H97" s="40" t="str">
+        <x:v>BurningOil</x:v>
+      </x:c>
+      <x:c r="I97"/>
+      <x:c r="J97" s="40" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K97" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98" s="40" t="str">
+        <x:v>FlameElbow</x:v>
+      </x:c>
+      <x:c r="I98"/>
+      <x:c r="J98" s="40" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K98" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99" s="40" t="str">
+        <x:v>SixHits</x:v>
+      </x:c>
+      <x:c r="I99"/>
+      <x:c r="J99" s="40" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K99" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
+      <x:c r="H100" s="40" t="str">
+        <x:v>TwelveHits</x:v>
+      </x:c>
+      <x:c r="I100"/>
+      <x:c r="J100" s="40" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K100" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L100"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101"/>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+      <x:c r="G101"/>
+      <x:c r="H101" s="40" t="str">
+        <x:v>QuickManeuver</x:v>
+      </x:c>
+      <x:c r="I101"/>
+      <x:c r="J101" s="40" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K101" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L101"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102"/>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+      <x:c r="G102"/>
+      <x:c r="H102" s="40" t="str">
+        <x:v>HoloDecoy</x:v>
+      </x:c>
+      <x:c r="I102"/>
+      <x:c r="J102" s="40" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K102" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L102"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
+      <x:c r="H103" s="40" t="str">
+        <x:v>LimitOverload</x:v>
+      </x:c>
+      <x:c r="I103"/>
+      <x:c r="J103" s="40" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K103" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L103"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+      <x:c r="G104"/>
+      <x:c r="H104" s="40" t="str">
+        <x:v>Machinegun</x:v>
+      </x:c>
+      <x:c r="I104"/>
+      <x:c r="J104" s="40" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K104" s="40" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
+      <x:c r="G105"/>
+      <x:c r="H105" s="62" t="str">
+        <x:v>DefenseTarget</x:v>
+      </x:c>
+      <x:c r="I105"/>
+      <x:c r="J105" s="62" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K105" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L105"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106" s="62" t="str">
+        <x:v>MachinegunBurst</x:v>
+      </x:c>
+      <x:c r="I106"/>
+      <x:c r="J106" s="62" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K106" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+      <x:c r="G107"/>
+      <x:c r="H107" s="62" t="str">
+        <x:v>TripleStrike</x:v>
+      </x:c>
+      <x:c r="I107"/>
+      <x:c r="J107" s="62" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K107" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+      <x:c r="G108"/>
+      <x:c r="H108" s="62" t="str">
+        <x:v>Bombard</x:v>
+      </x:c>
+      <x:c r="I108"/>
+      <x:c r="J108" s="62" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K108" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L108"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
+      <x:c r="G109"/>
+      <x:c r="H109" s="62" t="str">
+        <x:v>SkyWrath</x:v>
+      </x:c>
+      <x:c r="I109"/>
+      <x:c r="J109" s="62" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K109" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L109"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+      <x:c r="G110"/>
+      <x:c r="H110" s="62" t="str">
+        <x:v>PortableHelper</x:v>
+      </x:c>
+      <x:c r="I110"/>
+      <x:c r="J110" s="62" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K110" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+      <x:c r="G111"/>
+      <x:c r="H111" s="62" t="str">
+        <x:v>PrivateMod</x:v>
+      </x:c>
+      <x:c r="I111"/>
+      <x:c r="J111" s="62" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K111" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
+      <x:c r="G112"/>
+      <x:c r="H112" s="62" t="str">
+        <x:v>ChainSmoke</x:v>
+      </x:c>
+      <x:c r="I112"/>
+      <x:c r="J112" s="62" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K112" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L112"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
+      <x:c r="G113"/>
+      <x:c r="H113" s="62" t="str">
+        <x:v>SecondhandSmoke</x:v>
+      </x:c>
+      <x:c r="I113"/>
+      <x:c r="J113" s="62" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K113" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L113"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
+      <x:c r="G114"/>
+      <x:c r="H114" s="62" t="str">
+        <x:v>DefensiveStance</x:v>
+      </x:c>
+      <x:c r="I114"/>
+      <x:c r="J114" s="62" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K114" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L114"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+      <x:c r="G115"/>
+      <x:c r="H115" s="62" t="str">
+        <x:v>EmergencyCooling</x:v>
+      </x:c>
+      <x:c r="I115"/>
+      <x:c r="J115" s="62" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K115" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L115"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+      <x:c r="G116"/>
+      <x:c r="H116" s="62" t="str">
+        <x:v>ThermiteBomb</x:v>
+      </x:c>
+      <x:c r="I116"/>
+      <x:c r="J116" s="62" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K116" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L116"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
+      <x:c r="H117" s="62" t="str">
+        <x:v>NeedleStorm</x:v>
+      </x:c>
+      <x:c r="I117"/>
+      <x:c r="J117" s="62" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K117" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L117"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118"/>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+      <x:c r="G118"/>
+      <x:c r="H118" s="62" t="str">
+        <x:v>StealthAction</x:v>
+      </x:c>
+      <x:c r="I118"/>
+      <x:c r="J118" s="62" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K118" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L118"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119"/>
+      <x:c r="B119"/>
+      <x:c r="C119"/>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
+      <x:c r="F119"/>
+      <x:c r="G119"/>
+      <x:c r="H119" s="62" t="str">
+        <x:v>FoehnWind</x:v>
+      </x:c>
+      <x:c r="I119"/>
+      <x:c r="J119" s="62" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K119" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L119"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120"/>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
+      <x:c r="D120"/>
+      <x:c r="E120"/>
+      <x:c r="F120"/>
+      <x:c r="G120"/>
+      <x:c r="H120" s="62" t="str">
+        <x:v>PreemptiveStrike</x:v>
+      </x:c>
+      <x:c r="I120"/>
+      <x:c r="J120" s="62" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K120" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L120"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121"/>
+      <x:c r="B121"/>
+      <x:c r="C121"/>
+      <x:c r="D121"/>
+      <x:c r="E121"/>
+      <x:c r="F121"/>
+      <x:c r="G121"/>
+      <x:c r="H121" s="62" t="str">
+        <x:v>Bully</x:v>
+      </x:c>
+      <x:c r="I121"/>
+      <x:c r="J121" s="62" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K121" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L121"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122"/>
+      <x:c r="B122"/>
+      <x:c r="C122"/>
+      <x:c r="D122"/>
+      <x:c r="E122"/>
+      <x:c r="F122"/>
+      <x:c r="G122"/>
+      <x:c r="H122" s="62" t="str">
+        <x:v>PrismaticShot</x:v>
+      </x:c>
+      <x:c r="I122"/>
+      <x:c r="J122" s="62" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K122" s="62" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L122"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123"/>
+      <x:c r="B123"/>
+      <x:c r="C123"/>
+      <x:c r="D123"/>
+      <x:c r="E123"/>
+      <x:c r="F123"/>
+      <x:c r="G123"/>
+      <x:c r="H123" t="str">
+        <x:v>Mark</x:v>
+      </x:c>
+      <x:c r="I123"/>
+      <x:c r="J123" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L123"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124"/>
+      <x:c r="B124"/>
+      <x:c r="C124"/>
+      <x:c r="D124"/>
+      <x:c r="E124"/>
+      <x:c r="F124"/>
+      <x:c r="G124"/>
+      <x:c r="H124" t="str">
+        <x:v>Crush</x:v>
+      </x:c>
+      <x:c r="I124"/>
+      <x:c r="J124" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125"/>
+      <x:c r="B125"/>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+      <x:c r="F125"/>
+      <x:c r="G125"/>
+      <x:c r="H125" t="str">
+        <x:v>ChargedBurst</x:v>
+      </x:c>
+      <x:c r="I125"/>
+      <x:c r="J125" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="L125"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc13f6790b5de4446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe1e9fad382e4277"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3159,6 +3159,122 @@
       </x:c>
       <x:c r="L125"/>
     </x:row>
+    <x:row r="126">
+      <x:c r="A126"/>
+      <x:c r="B126" t="str">
+        <x:v>battle.CardUpgradeTrackKind</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E126"/>
+      <x:c r="F126" t="str">
+        <x:v>Card upgrade track kind</x:v>
+      </x:c>
+      <x:c r="G126"/>
+      <x:c r="H126" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I126"/>
+      <x:c r="J126" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>No G4 upgrade track</x:v>
+      </x:c>
+      <x:c r="L126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127"/>
+      <x:c r="B127"/>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127"/>
+      <x:c r="G127"/>
+      <x:c r="H127" t="str">
+        <x:v>Finite</x:v>
+      </x:c>
+      <x:c r="I127"/>
+      <x:c r="J127" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>Explicit sequential levels</x:v>
+      </x:c>
+      <x:c r="L127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128"/>
+      <x:c r="B128"/>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128"/>
+      <x:c r="G128"/>
+      <x:c r="H128" t="str">
+        <x:v>Infinite</x:v>
+      </x:c>
+      <x:c r="I128"/>
+      <x:c r="J128" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>Typed fixed delta per level</x:v>
+      </x:c>
+      <x:c r="L128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129"/>
+      <x:c r="B129" t="str">
+        <x:v>battle.CardUpgradeRuleKind</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E129"/>
+      <x:c r="F129" t="str">
+        <x:v>Typed card upgrade rule kind</x:v>
+      </x:c>
+      <x:c r="G129"/>
+      <x:c r="H129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I129"/>
+      <x:c r="J129" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>No numeric upgrade rule</x:v>
+      </x:c>
+      <x:c r="L129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130"/>
+      <x:c r="B130"/>
+      <x:c r="C130"/>
+      <x:c r="D130"/>
+      <x:c r="E130"/>
+      <x:c r="F130"/>
+      <x:c r="G130"/>
+      <x:c r="H130" t="str">
+        <x:v>DamageValue</x:v>
+      </x:c>
+      <x:c r="I130"/>
+      <x:c r="J130" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>Replace or add card damage value</x:v>
+      </x:c>
+      <x:c r="L130"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>
